--- a/docs/downloads/05/tbl_lighting_alaotra_mangabe.xlsx
+++ b/docs/downloads/05/tbl_lighting_alaotra_mangabe.xlsx
@@ -382,12 +382,6 @@
           <t>Alaotra - Mangabe</t>
         </is>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,12 +515,6 @@
           <t>Bois De Chauffe</t>
         </is>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -539,12 +527,6 @@
           <t>Electricité Réseau</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -556,12 +538,6 @@
         <is>
           <t>Groupe Électrogène</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>0.3</v>
       </c>
     </row>
     <row r="13">

--- a/docs/downloads/05/tbl_lighting_alaotra_mangabe.xlsx
+++ b/docs/downloads/05/tbl_lighting_alaotra_mangabe.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,7 +398,7 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>6.3</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="4">
@@ -409,14 +409,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>28.9</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="5">
@@ -427,14 +427,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="6">
@@ -445,32 +445,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pétrole Lampant</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>26.8</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Solaire</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>29.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="8">
@@ -479,11 +474,16 @@
           <t>Alaotra - Tous</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Batteries</t>
+        </is>
+      </c>
       <c r="C8">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D8">
-        <v>2.4</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="9">
@@ -494,14 +494,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Batteries</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>59</v>
-      </c>
-      <c r="D9">
-        <v>6.5</v>
+          <t>Bois De Chauffe</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -512,7 +506,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bois De Chauffe</t>
+          <t>Electricité Réseau</t>
         </is>
       </c>
     </row>
@@ -524,7 +518,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Electricité Réseau</t>
+          <t>Groupe Électrogène</t>
         </is>
       </c>
     </row>
@@ -536,8 +530,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Groupe Électrogène</t>
-        </is>
+          <t>Piles</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>63</v>
+      </c>
+      <c r="D12">
+        <v>12.4</v>
       </c>
     </row>
     <row r="13">
@@ -548,14 +548,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Panneau Solaire En Marche ?</t>
+          <t>Pétrole Lampant</t>
         </is>
       </c>
       <c r="C13">
-        <v>232</v>
+        <v>290</v>
       </c>
       <c r="D13">
-        <v>25.4</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="14">
@@ -566,50 +566,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Solaire</t>
         </is>
       </c>
       <c r="C14">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="D14">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Pétrole Lampant</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>290</v>
-      </c>
-      <c r="D15">
-        <v>31.8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Solaire</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>241</v>
-      </c>
-      <c r="D16">
-        <v>26.4</v>
+        <v>47.5</v>
       </c>
     </row>
   </sheetData>
